--- a/gebaeudedaten.xlsx
+++ b/gebaeudedaten.xlsx
@@ -8,19 +8,365 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://e1energie-my.sharepoint.com/personal/felix_rundel_e1-energie_com/Documents/2 Buero/6 GPT_Python/260225_Datenaufnahme/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_44DFE91D917E76CFEB3B98154B5DCE3AC7C946AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9386B17E-F394-487B-8377-BB12CCCA31CA}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_44DFE91D917E76CFEB3B98154B5DCE3AC7C946AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7178B23-9A18-4409-9BAF-C6B64C023D11}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Schwedenstraße" sheetId="1" r:id="rId1"/>
+    <sheet name="Polizeipräsidium Nordhessen" sheetId="2" r:id="rId1"/>
+    <sheet name="Schwedenstraße" sheetId="1" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Polizeipräsidium Nordhessen'!$A$1:$D$302</definedName>
+    <definedName name="Baseline_Arbeitspreis_Strom" localSheetId="0">[1]Baseline!$B$40</definedName>
+    <definedName name="Baseline_Arbeitspreis_Strom">[2]Baseline!$B$40</definedName>
+    <definedName name="Baseline_Leistungspreis_Strom" localSheetId="0">[1]Baseline!$B$42</definedName>
+    <definedName name="Baseline_Leistungspreis_Strom">[2]Baseline!$B$42</definedName>
+    <definedName name="TK_ABNR" hidden="1">"$ABNR"</definedName>
+    <definedName name="TK_AD" hidden="1">"$AD"</definedName>
+    <definedName name="TK_ADF" hidden="1">"$ADF"</definedName>
+    <definedName name="TK_ADFO" hidden="1">"$ADFO"</definedName>
+    <definedName name="TK_ADFOO" hidden="1">"$ADFOO"</definedName>
+    <definedName name="TK_ADO" hidden="1">"$ADO"</definedName>
+    <definedName name="TK_ADOTGEWST" hidden="1">"$ADOTGEWST"</definedName>
+    <definedName name="TK_ADOTGEWSTF" hidden="1">"$ADOTGEWSTF"</definedName>
+    <definedName name="TK_AG" hidden="1">"$AG"</definedName>
+    <definedName name="TK_AGS" hidden="1">"$AGS"</definedName>
+    <definedName name="TK_ALNR" hidden="1">"$ALNR"</definedName>
+    <definedName name="TK_AZ" hidden="1">"$AZ"</definedName>
+    <definedName name="TK_B1" hidden="1">"$B1"</definedName>
+    <definedName name="TK_B1ANREDE" hidden="1">"$B1ANREDE"</definedName>
+    <definedName name="TK_B1FNO" hidden="1">"$B1FNO"</definedName>
+    <definedName name="TK_B1FOO" hidden="1">"$B1FOO"</definedName>
+    <definedName name="TK_B1O" hidden="1">"$B1O"</definedName>
+    <definedName name="TK_B2" hidden="1">"$B2"</definedName>
+    <definedName name="TK_B2ANREDE" hidden="1">"$B2ANREDE"</definedName>
+    <definedName name="TK_B2FNO" hidden="1">"$B2FNO"</definedName>
+    <definedName name="TK_B2FOO" hidden="1">"$B2FOO"</definedName>
+    <definedName name="TK_B2O" hidden="1">"$B2O"</definedName>
+    <definedName name="TK_BE" hidden="1">"$BE"</definedName>
+    <definedName name="TK_BEF" hidden="1">"$BEF"</definedName>
+    <definedName name="TK_BEFANREDE1" hidden="1">"$BEFANREDE1"</definedName>
+    <definedName name="TK_BEFANREDE2" hidden="1">"$BEFANREDE2"</definedName>
+    <definedName name="TK_BEFEGNACHNAME" hidden="1">"$BEFEGNACHNAME"</definedName>
+    <definedName name="TK_BEFEGNAMENSBESTANDTEIL" hidden="1">"$BEFEGNAMENSBESTANDTEIL"</definedName>
+    <definedName name="TK_BEFEGTITEL" hidden="1">"$BEFEGTITEL"</definedName>
+    <definedName name="TK_BEFEGVORNAME" hidden="1">"$BEFEGVORNAME"</definedName>
+    <definedName name="TK_BEFG" hidden="1">"$BEFG"</definedName>
+    <definedName name="TK_BEFNACHNAMENZ1" hidden="1">"$BEFNACHNAMENZ1"</definedName>
+    <definedName name="TK_BEFNAME" hidden="1">"$BEFNAME"</definedName>
+    <definedName name="TK_BEFNAMENSBESTANDTEILNZ3" hidden="1">"$BEFNAMENSBESTANDTEILNZ3"</definedName>
+    <definedName name="TK_BEFO" hidden="1">"$BEFO"</definedName>
+    <definedName name="TK_BEFOG" hidden="1">"$BEFOG"</definedName>
+    <definedName name="TK_BEFORT" hidden="1">"$BEFORT"</definedName>
+    <definedName name="TK_BEFORTO" hidden="1">"$BEFORTO"</definedName>
+    <definedName name="TK_BEFORTSTEIL" hidden="1">"$BEFORTSTEIL"</definedName>
+    <definedName name="TK_BEFPLZ" hidden="1">"$BEFPLZ"</definedName>
+    <definedName name="TK_BEFSTAAT" hidden="1">"$BEFSTAAT"</definedName>
+    <definedName name="TK_BEFSTRASSE" hidden="1">"$BEFSTRASSE"</definedName>
+    <definedName name="TK_BEFSTRASSEPOFA" hidden="1">"$BEFSTRASSEPOFA"</definedName>
+    <definedName name="TK_BEFTITELNZ4" hidden="1">"$BEFTITELNZ4"</definedName>
+    <definedName name="TK_BEFVORNAMENZ2" hidden="1">"$BEFVORNAMENZ2"</definedName>
+    <definedName name="TK_BEG" hidden="1">"$BEG"</definedName>
+    <definedName name="TK_BENAME" hidden="1">"$BENAME"</definedName>
+    <definedName name="TK_BEO" hidden="1">"$BEO"</definedName>
+    <definedName name="TK_BEOG" hidden="1">"$BEOG"</definedName>
+    <definedName name="TK_BEORT" hidden="1">"$BEORT"</definedName>
+    <definedName name="TK_BERUF" hidden="1">"$BERUF"</definedName>
+    <definedName name="TK_BGLST" hidden="1">"$BGLST"</definedName>
+    <definedName name="TK_BIC1" hidden="1">"$BIC1"</definedName>
+    <definedName name="TK_BIC2" hidden="1">"$BIC2"</definedName>
+    <definedName name="TK_BILST1" hidden="1">"$BILST1"</definedName>
+    <definedName name="TK_BILST2" hidden="1">"$BILST2"</definedName>
+    <definedName name="TK_BILST3" hidden="1">"$BILST3"</definedName>
+    <definedName name="TK_BILST4" hidden="1">"$BILST4"</definedName>
+    <definedName name="TK_BILST5" hidden="1">"$BILST5"</definedName>
+    <definedName name="TK_BILST6" hidden="1">"$BILST6"</definedName>
+    <definedName name="TK_BK1" hidden="1">"$BK1"</definedName>
+    <definedName name="TK_BK1ABWINH" hidden="1">"$BK1ABWINH"</definedName>
+    <definedName name="TK_BK2" hidden="1">"$BK2"</definedName>
+    <definedName name="TK_BK2ABWINH" hidden="1">"$BK2ABWINH"</definedName>
+    <definedName name="TK_BLZ1" hidden="1">"$BLZ1"</definedName>
+    <definedName name="TK_BLZ2" hidden="1">"$BLZ2"</definedName>
+    <definedName name="TK_BN" hidden="1">"$BN"</definedName>
+    <definedName name="TK_BNO" hidden="1">"$BNO"</definedName>
+    <definedName name="TK_BPGKLGEW" hidden="1">"$BPGKLGEW"</definedName>
+    <definedName name="TK_BPGKLLUF" hidden="1">"$BPGKLLUF"</definedName>
+    <definedName name="TK_BPVGEW" hidden="1">"$BPVGEW"</definedName>
+    <definedName name="TK_BPVLUF" hidden="1">"$BPVLUF"</definedName>
+    <definedName name="TK_BVN" hidden="1">"$BVN"</definedName>
+    <definedName name="TK_BVNO" hidden="1">"$BVNO"</definedName>
+    <definedName name="TK_DA" hidden="1">"$DA"</definedName>
+    <definedName name="TK_DAPA" hidden="1">"$DAPA"</definedName>
+    <definedName name="TK_DAPB" hidden="1">"$DAPB"</definedName>
+    <definedName name="TK_DBEZ" hidden="1">"$DBEZ"</definedName>
+    <definedName name="TK_DMBIS" hidden="1">"$DMBIS"</definedName>
+    <definedName name="TK_DOKVAR_LAST_SHEET" hidden="1">"Investition"</definedName>
+    <definedName name="TK_EG" hidden="1">"$EG"</definedName>
+    <definedName name="TK_EGF" hidden="1">"$EGF"</definedName>
+    <definedName name="TK_EGFNACHNAME" hidden="1">"$EGFNACHNAME"</definedName>
+    <definedName name="TK_EGFNAMENSBESTANDTEIL" hidden="1">"$EGFNAMENSBESTANDTEIL"</definedName>
+    <definedName name="TK_EGFO" hidden="1">"$EGFO"</definedName>
+    <definedName name="TK_EGFTITEL" hidden="1">"$EGFTITEL"</definedName>
+    <definedName name="TK_EGFVORNAME" hidden="1">"$EGFVORNAME"</definedName>
+    <definedName name="TK_EGO" hidden="1">"$EGO"</definedName>
+    <definedName name="TK_EMAILAG" hidden="1">"$EMAILAG"</definedName>
+    <definedName name="TK_EMAILPERS" hidden="1">"$EMAILPERS"</definedName>
+    <definedName name="TK_EMAILSTB" hidden="1">"$EMAILSTB"</definedName>
+    <definedName name="TK_EMPF" hidden="1">"$EMPF"</definedName>
+    <definedName name="TK_EMPFF" hidden="1">"$EMPFF"</definedName>
+    <definedName name="TK_EMPFFANREDE" hidden="1">"$EMPFFANREDE"</definedName>
+    <definedName name="TK_EMPFFEGNACHNAME" hidden="1">"$EMPFFEGNACHNAME"</definedName>
+    <definedName name="TK_EMPFFEGNAMENSBESTANDTEIL" hidden="1">"$EMPFFEGNAMENSBESTANDTEIL"</definedName>
+    <definedName name="TK_EMPFFEGTITEL" hidden="1">"$EMPFFEGTITEL"</definedName>
+    <definedName name="TK_EMPFFEGVORNAME" hidden="1">"$EMPFFEGVORNAME"</definedName>
+    <definedName name="TK_EMPFFG" hidden="1">"$EMPFFG"</definedName>
+    <definedName name="TK_EMPFFNACHNAMENZ1" hidden="1">"$EMPFFNACHNAMENZ1"</definedName>
+    <definedName name="TK_EMPFFNAMENSBESTANDTEILNZ3" hidden="1">"$EMPFFNAMENSBESTANDTEILNZ3"</definedName>
+    <definedName name="TK_EMPFFO" hidden="1">"$EMPFFO"</definedName>
+    <definedName name="TK_EMPFFOG" hidden="1">"$EMPFFOG"</definedName>
+    <definedName name="TK_EMPFFORTO" hidden="1">"$EMPFFORTO"</definedName>
+    <definedName name="TK_EMPFFORTSTEIL" hidden="1">"$EMPFFORTSTEIL"</definedName>
+    <definedName name="TK_EMPFFPLZ" hidden="1">"$EMPFFPLZ"</definedName>
+    <definedName name="TK_EMPFFSTAAT" hidden="1">"$EMPFFSTAAT"</definedName>
+    <definedName name="TK_EMPFFSTRASSEPOFA" hidden="1">"$EMPFFSTRASSEPOFA"</definedName>
+    <definedName name="TK_EMPFFTITELNZ4" hidden="1">"$EMPFFTITELNZ4"</definedName>
+    <definedName name="TK_EMPFFVORNAMENZ2" hidden="1">"$EMPFFVORNAMENZ2"</definedName>
+    <definedName name="TK_EMPFG" hidden="1">"$EMPFG"</definedName>
+    <definedName name="TK_EMPFO" hidden="1">"$EMPFO"</definedName>
+    <definedName name="TK_EMPFOG" hidden="1">"$EMPFOG"</definedName>
+    <definedName name="TK_FA" hidden="1">"$FA"</definedName>
+    <definedName name="TK_FABIC" hidden="1">"$FABIC"</definedName>
+    <definedName name="TK_FABIC2" hidden="1">"$FABIC2"</definedName>
+    <definedName name="TK_FABIC3" hidden="1">"$FABIC3"</definedName>
+    <definedName name="TK_FABK" hidden="1">"$FABK"</definedName>
+    <definedName name="TK_FABK2" hidden="1">"$FABK2"</definedName>
+    <definedName name="TK_FABK3" hidden="1">"$FABK3"</definedName>
+    <definedName name="TK_FABLZ" hidden="1">"$FABLZ"</definedName>
+    <definedName name="TK_FABLZ2" hidden="1">"$FABLZ2"</definedName>
+    <definedName name="TK_FABLZ3" hidden="1">"$FABLZ3"</definedName>
+    <definedName name="TK_FAEMAIL" hidden="1">"$FAEMAIL"</definedName>
+    <definedName name="TK_FAGLAEUBID" hidden="1">"$FAGLAEUBID"</definedName>
+    <definedName name="TK_FAGROSSORT" hidden="1">"$FAGROSSORT"</definedName>
+    <definedName name="TK_FAGROSSPLZ" hidden="1">"$FAGROSSPLZ"</definedName>
+    <definedName name="TK_FAHALTART1" hidden="1">"$FAHALTART1"</definedName>
+    <definedName name="TK_FAHALTART2" hidden="1">"$FAHALTART2"</definedName>
+    <definedName name="TK_FAHALTART3" hidden="1">"$FAHALTART3"</definedName>
+    <definedName name="TK_FAHALTART4" hidden="1">"$FAHALTART4"</definedName>
+    <definedName name="TK_FAHALTART5" hidden="1">"$FAHALTART5"</definedName>
+    <definedName name="TK_FAHALTART6" hidden="1">"$FAHALTART6"</definedName>
+    <definedName name="TK_FAHALTBEZ1" hidden="1">"$FAHALTBEZ1"</definedName>
+    <definedName name="TK_FAHALTBEZ2" hidden="1">"$FAHALTBEZ2"</definedName>
+    <definedName name="TK_FAHALTBEZ3" hidden="1">"$FAHALTBEZ3"</definedName>
+    <definedName name="TK_FAHALTBEZ4" hidden="1">"$FAHALTBEZ4"</definedName>
+    <definedName name="TK_FAHALTBEZ5" hidden="1">"$FAHALTBEZ5"</definedName>
+    <definedName name="TK_FAHALTBEZ6" hidden="1">"$FAHALTBEZ6"</definedName>
+    <definedName name="TK_FAHAUSADR" hidden="1">"$FAHAUSADR"</definedName>
+    <definedName name="TK_FAHAUSADRF" hidden="1">"$FAHAUSADRF"</definedName>
+    <definedName name="TK_FAIBAN" hidden="1">"$FAIBAN"</definedName>
+    <definedName name="TK_FAIBAN2" hidden="1">"$FAIBAN2"</definedName>
+    <definedName name="TK_FAIBAN3" hidden="1">"$FAIBAN3"</definedName>
+    <definedName name="TK_FAINTERNET" hidden="1">"$FAINTERNET"</definedName>
+    <definedName name="TK_FAKTNR" hidden="1">"$FAKTNR"</definedName>
+    <definedName name="TK_FAKTNR2" hidden="1">"$FAKTNR2"</definedName>
+    <definedName name="TK_FAKTNR3" hidden="1">"$FAKTNR3"</definedName>
+    <definedName name="TK_FALIEFADR" hidden="1">"$FALIEFADR"</definedName>
+    <definedName name="TK_FALIEFADRF" hidden="1">"$FALIEFADRF"</definedName>
+    <definedName name="TK_FANR3" hidden="1">"$FANR3"</definedName>
+    <definedName name="TK_FANR4" hidden="1">"$FANR4"</definedName>
+    <definedName name="TK_FAO" hidden="1">"$FAO"</definedName>
+    <definedName name="TK_FAOA" hidden="1">"$FAOA"</definedName>
+    <definedName name="TK_FAOOA" hidden="1">"$FAOOA"</definedName>
+    <definedName name="TK_FAPOFAFACH" hidden="1">"$FAPOFAFACH"</definedName>
+    <definedName name="TK_FAPOFAORT" hidden="1">"$FAPOFAORT"</definedName>
+    <definedName name="TK_FAPOFAPLZ" hidden="1">"$FAPOFAPLZ"</definedName>
+    <definedName name="TK_FARUECKADR" hidden="1">"$FARUECKADR"</definedName>
+    <definedName name="TK_FARUECKADRF" hidden="1">"$FARUECKADRF"</definedName>
+    <definedName name="TK_FASPRECHBESCH" hidden="1">"$FASPRECHBESCH"</definedName>
+    <definedName name="TK_FASPRECHBESCH2" hidden="1">"$FASPRECHBESCH2"</definedName>
+    <definedName name="TK_FASPRECHBESCH3" hidden="1">"$FASPRECHBESCH3"</definedName>
+    <definedName name="TK_FASPRECHBESCH4" hidden="1">"$FASPRECHBESCH4"</definedName>
+    <definedName name="TK_FASPRECHVONBIS" hidden="1">"$FASPRECHVONBIS"</definedName>
+    <definedName name="TK_FASPRECHVONBIS2" hidden="1">"$FASPRECHVONBIS2"</definedName>
+    <definedName name="TK_FASPRECHVONBIS3" hidden="1">"$FASPRECHVONBIS3"</definedName>
+    <definedName name="TK_FASPRECHVONBIS4" hidden="1">"$FASPRECHVONBIS4"</definedName>
+    <definedName name="TK_FAXFA" hidden="1">"$FAXFA"</definedName>
+    <definedName name="TK_FAXGEBAEUDETEIL" hidden="1">"$FAXGEBAEUDETEIL"</definedName>
+    <definedName name="TK_FAXGESCHAEFTSANGABEN" hidden="1">"$FAXGESCHAEFTSANGABEN"</definedName>
+    <definedName name="TK_FAXXXX" hidden="1">"$FAXXXX"</definedName>
+    <definedName name="TK_FAXXXXF" hidden="1">"$FAXXXXF"</definedName>
+    <definedName name="TK_FAXXXXNA" hidden="1">"$FAXXXXNA"</definedName>
+    <definedName name="TK_FI" hidden="1">"$FI"</definedName>
+    <definedName name="TK_FIAF" hidden="1">"$FIAF"</definedName>
+    <definedName name="TK_FIF" hidden="1">"$FIF"</definedName>
+    <definedName name="TK_FINF" hidden="1">"$FINF"</definedName>
+    <definedName name="TK_FIO" hidden="1">"$FIO"</definedName>
+    <definedName name="TK_FIOF" hidden="1">"$FIOF"</definedName>
+    <definedName name="TK_FREI1" hidden="1">"$FREI1"</definedName>
+    <definedName name="TK_FUER" hidden="1">"$FUER"</definedName>
+    <definedName name="TK_FUERF" hidden="1">"$FUERF"</definedName>
+    <definedName name="TK_FUERFANREDE" hidden="1">"$FUERFANREDE"</definedName>
+    <definedName name="TK_FUERFEGNACHNAME" hidden="1">"$FUERFEGNACHNAME"</definedName>
+    <definedName name="TK_FUERFEGNAMENSBESTANDTEIL" hidden="1">"$FUERFEGNAMENSBESTANDTEIL"</definedName>
+    <definedName name="TK_FUERFEGTITEL" hidden="1">"$FUERFEGTITEL"</definedName>
+    <definedName name="TK_FUERFEGVORNAME" hidden="1">"$FUERFEGVORNAME"</definedName>
+    <definedName name="TK_FUERFG" hidden="1">"$FUERFG"</definedName>
+    <definedName name="TK_FUERFNACHNAMENZ1" hidden="1">"$FUERFNACHNAMENZ1"</definedName>
+    <definedName name="TK_FUERFNAMENSBESTANDTEILNZ3" hidden="1">"$FUERFNAMENSBESTANDTEILNZ3"</definedName>
+    <definedName name="TK_FUERFO" hidden="1">"$FUERFO"</definedName>
+    <definedName name="TK_FUERFOG" hidden="1">"$FUERFOG"</definedName>
+    <definedName name="TK_FUERFORTO" hidden="1">"$FUERFORTO"</definedName>
+    <definedName name="TK_FUERFORTSTEIL" hidden="1">"$FUERFORTSTEIL"</definedName>
+    <definedName name="TK_FUERFPLZ" hidden="1">"$FUERFPLZ"</definedName>
+    <definedName name="TK_FUERFSTAAT" hidden="1">"$FUERFSTAAT"</definedName>
+    <definedName name="TK_FUERFSTRASSEPOFA" hidden="1">"$FUERFSTRASSEPOFA"</definedName>
+    <definedName name="TK_FUERFTITELNZ4" hidden="1">"$FUERFTITELNZ4"</definedName>
+    <definedName name="TK_FUERFVORNAMENZ2" hidden="1">"$FUERFVORNAMENZ2"</definedName>
+    <definedName name="TK_FUERG" hidden="1">"$FUERG"</definedName>
+    <definedName name="TK_FUERO" hidden="1">"$FUERO"</definedName>
+    <definedName name="TK_FUEROG" hidden="1">"$FUEROG"</definedName>
+    <definedName name="TK_FÜR" hidden="1">"$FÜR"</definedName>
+    <definedName name="TK_FÜRF" hidden="1">"$FÜRF"</definedName>
+    <definedName name="TK_FÜRFANREDE" hidden="1">"$FÜRFANREDE"</definedName>
+    <definedName name="TK_FÜRFEGNACHNAME" hidden="1">"$FÜRFEGNACHNAME"</definedName>
+    <definedName name="TK_FÜRFEGNAMENSBESTANDTEIL" hidden="1">"$FÜRFEGNAMENSBESTANDTEIL"</definedName>
+    <definedName name="TK_FÜRFEGTITEL" hidden="1">"$FÜRFEGTITEL"</definedName>
+    <definedName name="TK_FÜRFEGVORNAME" hidden="1">"$FÜRFEGVORNAME"</definedName>
+    <definedName name="TK_FÜRFG" hidden="1">"$FÜRFG"</definedName>
+    <definedName name="TK_FÜRFNACHNAMENZ1" hidden="1">"$FÜRFNACHNAMENZ1"</definedName>
+    <definedName name="TK_FÜRFNAMENSBESTANDTEILNZ3" hidden="1">"$FÜRFNAMENSBESTANDTEILNZ3"</definedName>
+    <definedName name="TK_FÜRFO" hidden="1">"$FÜRFO"</definedName>
+    <definedName name="TK_FÜRFOG" hidden="1">"$FÜRFOG"</definedName>
+    <definedName name="TK_FÜRFORTO" hidden="1">"$FÜRFORTO"</definedName>
+    <definedName name="TK_FÜRFORTSTEIL" hidden="1">"$FÜRFORTSTEIL"</definedName>
+    <definedName name="TK_FÜRFPLZ" hidden="1">"$FÜRFPLZ"</definedName>
+    <definedName name="TK_FÜRFSTAAT" hidden="1">"$FÜRFSTAAT"</definedName>
+    <definedName name="TK_FÜRFSTRASSEPOFA" hidden="1">"$FÜRFSTRASSEPOFA"</definedName>
+    <definedName name="TK_FÜRFTITELNZ4" hidden="1">"$FÜRFTITELNZ4"</definedName>
+    <definedName name="TK_FÜRFVORNAMENZ2" hidden="1">"$FÜRFVORNAMENZ2"</definedName>
+    <definedName name="TK_FÜRG" hidden="1">"$FÜRG"</definedName>
+    <definedName name="TK_FÜRO" hidden="1">"$FÜRO"</definedName>
+    <definedName name="TK_FÜROG" hidden="1">"$FÜROG"</definedName>
+    <definedName name="TK_FX" hidden="1">"$FX"</definedName>
+    <definedName name="TK_FXAD" hidden="1">"$FXAD"</definedName>
+    <definedName name="TK_FXEINWAHL" hidden="1">"$FXEINWAHL"</definedName>
+    <definedName name="TK_FXSTB" hidden="1">"$FXSTB"</definedName>
+    <definedName name="TK_FXVORWAHL" hidden="1">"$FXVORWAHL"</definedName>
+    <definedName name="TK_GD" hidden="1">"$GD"</definedName>
+    <definedName name="TK_GDBE" hidden="1">"$GDBE"</definedName>
+    <definedName name="TK_GDEMPF" hidden="1">"$GDEMPF"</definedName>
+    <definedName name="TK_GDFUER" hidden="1">"$GDFUER"</definedName>
+    <definedName name="TK_GDFÜR" hidden="1">"$GDFÜR"</definedName>
+    <definedName name="TK_GE" hidden="1">"$GE"</definedName>
+    <definedName name="TK_GEWBEZ" hidden="1">"$GEWBEZ"</definedName>
+    <definedName name="TK_GEWKZ" hidden="1">"$GEWKZ"</definedName>
+    <definedName name="TK_GG" hidden="1">"$GG"</definedName>
+    <definedName name="TK_GIBGKL" hidden="1">"$GIBGKL"</definedName>
+    <definedName name="TK_HINW1" hidden="1">"$HINW1"</definedName>
+    <definedName name="TK_HINW2" hidden="1">"$HINW2"</definedName>
+    <definedName name="TK_HINW3" hidden="1">"$HINW3"</definedName>
+    <definedName name="TK_IBAN1" hidden="1">"$IBAN1"</definedName>
+    <definedName name="TK_IBAN2" hidden="1">"$IBAN2"</definedName>
+    <definedName name="TK_ID" hidden="1">"$ID"</definedName>
+    <definedName name="TK_IDEG" hidden="1">"$IDEG"</definedName>
+    <definedName name="TK_IDG" hidden="1">"$IDG"</definedName>
+    <definedName name="TK_KFZANMDAT" hidden="1">"$KFZANMDAT"</definedName>
+    <definedName name="TK_KFZART" hidden="1">"$KFZART"</definedName>
+    <definedName name="TK_KFZERSTZUL" hidden="1">"$KFZERSTZUL"</definedName>
+    <definedName name="TK_KFZGESTELL" hidden="1">"$KFZGESTELL"</definedName>
+    <definedName name="TK_KFZGEW" hidden="1">"$KFZGEW"</definedName>
+    <definedName name="TK_KFZHBEZ" hidden="1">"$KFZHBEZ"</definedName>
+    <definedName name="TK_KFZHERSTNR" hidden="1">"$KFZHERSTNR"</definedName>
+    <definedName name="TK_KFZHUB" hidden="1">"$KFZHUB"</definedName>
+    <definedName name="TK_KFZTYP" hidden="1">"$KFZTYP"</definedName>
+    <definedName name="TK_KONZNR" hidden="1">"$KONZNR"</definedName>
+    <definedName name="TK_KTNR1" hidden="1">"$KTNR1"</definedName>
+    <definedName name="TK_KTNR2" hidden="1">"$KTNR2"</definedName>
+    <definedName name="TK_MANDREF1" hidden="1">"$MANDREF1"</definedName>
+    <definedName name="TK_MANDREF2" hidden="1">"$MANDREF2"</definedName>
+    <definedName name="TK_NA" hidden="1">"$NA"</definedName>
+    <definedName name="TK_NA4F" hidden="1">"$NA4F"</definedName>
+    <definedName name="TK_NAEG" hidden="1">"$NAEG"</definedName>
+    <definedName name="TK_NAEGNN" hidden="1">"$NAEGNN"</definedName>
+    <definedName name="TK_NAEGNT" hidden="1">"$NAEGNT"</definedName>
+    <definedName name="TK_NAEGNV" hidden="1">"$NAEGNV"</definedName>
+    <definedName name="TK_NAEGV" hidden="1">"$NAEGV"</definedName>
+    <definedName name="TK_NANN" hidden="1">"$NANN"</definedName>
+    <definedName name="TK_NANT" hidden="1">"$NANT"</definedName>
+    <definedName name="TK_NANV" hidden="1">"$NANV"</definedName>
+    <definedName name="TK_NAV" hidden="1">"$NAV"</definedName>
+    <definedName name="TK_NAVNAEGV" hidden="1">"$NAVNAEGV"</definedName>
+    <definedName name="TK_OFD" hidden="1">"$OFD"</definedName>
+    <definedName name="TK_ORT" hidden="1">"$ORT"</definedName>
+    <definedName name="TK_ORTLIEF" hidden="1">"$ORTLIEF"</definedName>
+    <definedName name="TK_ORTRUECK" hidden="1">"$ORTRUECK"</definedName>
+    <definedName name="TK_PA" hidden="1">"$PA"</definedName>
+    <definedName name="TK_PAZ" hidden="1">"$PAZ"</definedName>
+    <definedName name="TK_PF" hidden="1">"$PF"</definedName>
+    <definedName name="TK_PFA" hidden="1">"$PFA"</definedName>
+    <definedName name="TK_PFF" hidden="1">"$PFF"</definedName>
+    <definedName name="TK_PFFO" hidden="1">"$PFFO"</definedName>
+    <definedName name="TK_PFO" hidden="1">"$PFO"</definedName>
+    <definedName name="TK_PLZ" hidden="1">"$PLZ"</definedName>
+    <definedName name="TK_PLZLIEF" hidden="1">"$PLZLIEF"</definedName>
+    <definedName name="TK_PLZRUECK" hidden="1">"$PLZRUECK"</definedName>
+    <definedName name="TK_PN" hidden="1">"$PN"</definedName>
+    <definedName name="TK_PORG" hidden="1">"$PORG"</definedName>
+    <definedName name="TK_PRB" hidden="1">"$PRB"</definedName>
+    <definedName name="TK_PSM" hidden="1">"$PSM"</definedName>
+    <definedName name="TK_PSTA" hidden="1">"$PSTA"</definedName>
+    <definedName name="TK_PV" hidden="1">"$PV"</definedName>
+    <definedName name="TK_PZR" hidden="1">"$PZR"</definedName>
+    <definedName name="TK_PZRB" hidden="1">"$PZRB"</definedName>
+    <definedName name="TK_PZRE" hidden="1">"$PZRE"</definedName>
+    <definedName name="TK_PZRERTRAG" hidden="1">"$PZRERTRAG"</definedName>
+    <definedName name="TK_PZREW" hidden="1">"$PZREW"</definedName>
+    <definedName name="TK_PZRJ1" hidden="1">"$PZRJ1"</definedName>
+    <definedName name="TK_PZRJ1ERTRAG" hidden="1">"$PZRJ1ERTRAG"</definedName>
+    <definedName name="TK_PZRJ1EW" hidden="1">"$PZRJ1EW"</definedName>
+    <definedName name="TK_PZRJ1SONST" hidden="1">"$PZRJ1SONST"</definedName>
+    <definedName name="TK_PZRJ1UST" hidden="1">"$PZRJ1UST"</definedName>
+    <definedName name="TK_PZRLJBP" hidden="1">"$PZRLJBP"</definedName>
+    <definedName name="TK_PZRSONST" hidden="1">"$PZRSONST"</definedName>
+    <definedName name="TK_PZRUST" hidden="1">"$PZRUST"</definedName>
+    <definedName name="TK_REFORM" hidden="1">"$REFORM"</definedName>
+    <definedName name="TK_REFORMAB" hidden="1">"$REFORMAB"</definedName>
+    <definedName name="TK_ST" hidden="1">"$ST"</definedName>
+    <definedName name="TK_STB" hidden="1">"$STB"</definedName>
+    <definedName name="TK_STBAB" hidden="1">"$STBAB"</definedName>
+    <definedName name="TK_STBF" hidden="1">"$STBF"</definedName>
+    <definedName name="TK_STBFO" hidden="1">"$STBFO"</definedName>
+    <definedName name="TK_STBO" hidden="1">"$STBO"</definedName>
+    <definedName name="TK_STO" hidden="1">"$STO"</definedName>
+    <definedName name="TK_STOTGEWST" hidden="1">"$STOTGEWST"</definedName>
+    <definedName name="TK_STOTUST" hidden="1">"$STOTUST"</definedName>
+    <definedName name="TK_STRASSE" hidden="1">"$STRASSE"</definedName>
+    <definedName name="TK_STRASSELIEF" hidden="1">"$STRASSELIEF"</definedName>
+    <definedName name="TK_STRASSERUECK" hidden="1">"$STRASSERUECK"</definedName>
+    <definedName name="TK_TL" hidden="1">"$TL"</definedName>
+    <definedName name="TK_TLAD" hidden="1">"$TLAD"</definedName>
+    <definedName name="TK_TLFA" hidden="1">"$TLFA"</definedName>
+    <definedName name="TK_TLSTB" hidden="1">"$TLSTB"</definedName>
+    <definedName name="TK_TLVERM" hidden="1">"$TLVERM"</definedName>
+    <definedName name="TK_USTIDNR" hidden="1">"$USTIDNR"</definedName>
+    <definedName name="TK_VFA" hidden="1">"$VFA"</definedName>
+    <definedName name="TK_WAEHRUNG" hidden="1">"$Waehrung"</definedName>
+    <definedName name="TK_WÄHRUNG" hidden="1">"$Währung"</definedName>
+    <definedName name="TK_ZI" hidden="1">"$ZI"</definedName>
+    <definedName name="TK_ZWANGOBJEKT" hidden="1">"$ZWANGOBJEKT"</definedName>
+    <definedName name="TK_ZWG1" hidden="1">"$ZWG1"</definedName>
+    <definedName name="TK_ZWG2" hidden="1">"$ZWG2"</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="1296">
   <si>
     <t>Gebäude</t>
   </si>
@@ -2867,13 +3213,1057 @@
   </si>
   <si>
     <t>0.82</t>
+  </si>
+  <si>
+    <t>Geschoss</t>
+  </si>
+  <si>
+    <t>Raum Nr.</t>
+  </si>
+  <si>
+    <t>Raumbezeichnung</t>
+  </si>
+  <si>
+    <t>Bodenfläche</t>
+  </si>
+  <si>
+    <t>E415</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>E416</t>
+  </si>
+  <si>
+    <t>E507</t>
+  </si>
+  <si>
+    <t>Ruheraum</t>
+  </si>
+  <si>
+    <t>E508</t>
+  </si>
+  <si>
+    <t>E609a</t>
+  </si>
+  <si>
+    <t>Vorraum WC</t>
+  </si>
+  <si>
+    <t>E960</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Umkleide</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>1109b</t>
+  </si>
+  <si>
+    <t>WC-H</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>1111a</t>
+  </si>
+  <si>
+    <t>1111b</t>
+  </si>
+  <si>
+    <t>Duschen</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Trockenraum</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1115a</t>
+  </si>
+  <si>
+    <t>1115b</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>WC-D</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>Dusche</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>1305</t>
+  </si>
+  <si>
+    <t>1306</t>
+  </si>
+  <si>
+    <t>1401a</t>
+  </si>
+  <si>
+    <t>Fotolabor</t>
+  </si>
+  <si>
+    <t>1401b</t>
+  </si>
+  <si>
+    <t>1401c</t>
+  </si>
+  <si>
+    <t>1401d</t>
+  </si>
+  <si>
+    <t>1402</t>
+  </si>
+  <si>
+    <t>1403</t>
+  </si>
+  <si>
+    <t>1404</t>
+  </si>
+  <si>
+    <t>1405</t>
+  </si>
+  <si>
+    <t>Wache</t>
+  </si>
+  <si>
+    <t>1406</t>
+  </si>
+  <si>
+    <t>1407</t>
+  </si>
+  <si>
+    <t>1408</t>
+  </si>
+  <si>
+    <t>1409</t>
+  </si>
+  <si>
+    <t>1410</t>
+  </si>
+  <si>
+    <t>1411</t>
+  </si>
+  <si>
+    <t>1412</t>
+  </si>
+  <si>
+    <t>1413</t>
+  </si>
+  <si>
+    <t>1414</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>1416</t>
+  </si>
+  <si>
+    <t>Funktionsraum</t>
+  </si>
+  <si>
+    <t>1417</t>
+  </si>
+  <si>
+    <t>1418</t>
+  </si>
+  <si>
+    <t>1419</t>
+  </si>
+  <si>
+    <t>1419a</t>
+  </si>
+  <si>
+    <t>1420</t>
+  </si>
+  <si>
+    <t>1420a</t>
+  </si>
+  <si>
+    <t>1421</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>1423</t>
+  </si>
+  <si>
+    <t>1424</t>
+  </si>
+  <si>
+    <t>Aktenraum</t>
+  </si>
+  <si>
+    <t>1425</t>
+  </si>
+  <si>
+    <t>1426</t>
+  </si>
+  <si>
+    <t>1427</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>1502</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>Haustechnik</t>
+  </si>
+  <si>
+    <t>1505</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>1507</t>
+  </si>
+  <si>
+    <t>Dusche-Vorr.</t>
+  </si>
+  <si>
+    <t>1509</t>
+  </si>
+  <si>
+    <t>Vorraum</t>
+  </si>
+  <si>
+    <t>1509a</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>1514</t>
+  </si>
+  <si>
+    <t>1516a</t>
+  </si>
+  <si>
+    <t>1516b</t>
+  </si>
+  <si>
+    <t>1517</t>
+  </si>
+  <si>
+    <t>1518</t>
+  </si>
+  <si>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>1520</t>
+  </si>
+  <si>
+    <t>1521</t>
+  </si>
+  <si>
+    <t>1522</t>
+  </si>
+  <si>
+    <t>1526</t>
+  </si>
+  <si>
+    <t>1527</t>
+  </si>
+  <si>
+    <t>1528</t>
+  </si>
+  <si>
+    <t>1529</t>
+  </si>
+  <si>
+    <t>Aufenthaltsr.</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>Kühlraum Fotolab.</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Waschraum</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Pumi</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Trocken</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Wäscheraum</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>Technikr.</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>Flur+Wartezone</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>2114</t>
+  </si>
+  <si>
+    <t>2115</t>
+  </si>
+  <si>
+    <t>2116</t>
+  </si>
+  <si>
+    <t>2117</t>
+  </si>
+  <si>
+    <t>2118</t>
+  </si>
+  <si>
+    <t>2119</t>
+  </si>
+  <si>
+    <t>2120</t>
+  </si>
+  <si>
+    <t>2121</t>
+  </si>
+  <si>
+    <t>2122</t>
+  </si>
+  <si>
+    <t>2123</t>
+  </si>
+  <si>
+    <t>2124</t>
+  </si>
+  <si>
+    <t>2125</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2413</t>
+  </si>
+  <si>
+    <t>2414</t>
+  </si>
+  <si>
+    <t>1.Hilfe</t>
+  </si>
+  <si>
+    <t>2415</t>
+  </si>
+  <si>
+    <t>Schulungsraum</t>
+  </si>
+  <si>
+    <t>2416</t>
+  </si>
+  <si>
+    <t>Versammlungsraum</t>
+  </si>
+  <si>
+    <t>2416a</t>
+  </si>
+  <si>
+    <t>2416b</t>
+  </si>
+  <si>
+    <t>Versammlungsr.</t>
+  </si>
+  <si>
+    <t>2417</t>
+  </si>
+  <si>
+    <t>Kantine</t>
+  </si>
+  <si>
+    <t>2418a</t>
+  </si>
+  <si>
+    <t>2418b</t>
+  </si>
+  <si>
+    <t>2418c</t>
+  </si>
+  <si>
+    <t>2419</t>
+  </si>
+  <si>
+    <t>WC Behinderte</t>
+  </si>
+  <si>
+    <t>2420</t>
+  </si>
+  <si>
+    <t>WC-Vorr.</t>
+  </si>
+  <si>
+    <t>2423</t>
+  </si>
+  <si>
+    <t>2424</t>
+  </si>
+  <si>
+    <t>2425</t>
+  </si>
+  <si>
+    <t>2426</t>
+  </si>
+  <si>
+    <t>2427</t>
+  </si>
+  <si>
+    <t>2428</t>
+  </si>
+  <si>
+    <t>2429</t>
+  </si>
+  <si>
+    <t>Hausdruckerei</t>
+  </si>
+  <si>
+    <t>2431</t>
+  </si>
+  <si>
+    <t>2432</t>
+  </si>
+  <si>
+    <t>2433</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2507a</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>Stuhllager</t>
+  </si>
+  <si>
+    <t>2514</t>
+  </si>
+  <si>
+    <t>2515</t>
+  </si>
+  <si>
+    <t>2516</t>
+  </si>
+  <si>
+    <t>Lager+Werkstatt</t>
+  </si>
+  <si>
+    <t>2517</t>
+  </si>
+  <si>
+    <t>Geräteausgabe</t>
+  </si>
+  <si>
+    <t>2519</t>
+  </si>
+  <si>
+    <t>2520</t>
+  </si>
+  <si>
+    <t>2521</t>
+  </si>
+  <si>
+    <t>2522</t>
+  </si>
+  <si>
+    <t>2523</t>
+  </si>
+  <si>
+    <t>Getränkelager</t>
+  </si>
+  <si>
+    <t>2524</t>
+  </si>
+  <si>
+    <t>Ausstellungsr.</t>
+  </si>
+  <si>
+    <t>2525</t>
+  </si>
+  <si>
+    <t>2970</t>
+  </si>
+  <si>
+    <t>3101</t>
+  </si>
+  <si>
+    <t>3113</t>
+  </si>
+  <si>
+    <t>Spindraum</t>
+  </si>
+  <si>
+    <t>3114</t>
+  </si>
+  <si>
+    <t>3115</t>
+  </si>
+  <si>
+    <t>3116</t>
+  </si>
+  <si>
+    <t>3117</t>
+  </si>
+  <si>
+    <t>3120</t>
+  </si>
+  <si>
+    <t>3121</t>
+  </si>
+  <si>
+    <t>3122</t>
+  </si>
+  <si>
+    <t>3123</t>
+  </si>
+  <si>
+    <t>3124</t>
+  </si>
+  <si>
+    <t>3302</t>
+  </si>
+  <si>
+    <t>Dusche H</t>
+  </si>
+  <si>
+    <t>3305</t>
+  </si>
+  <si>
+    <t>Dusche D</t>
+  </si>
+  <si>
+    <t>3306</t>
+  </si>
+  <si>
+    <t>4101</t>
+  </si>
+  <si>
+    <t>4102</t>
+  </si>
+  <si>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>4106</t>
+  </si>
+  <si>
+    <t>4107</t>
+  </si>
+  <si>
+    <t>4108</t>
+  </si>
+  <si>
+    <t>4109</t>
+  </si>
+  <si>
+    <t>4110</t>
+  </si>
+  <si>
+    <t>4111</t>
+  </si>
+  <si>
+    <t>4113</t>
+  </si>
+  <si>
+    <t>4115</t>
+  </si>
+  <si>
+    <t>4116</t>
+  </si>
+  <si>
+    <t>4117</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>4119</t>
+  </si>
+  <si>
+    <t>4120</t>
+  </si>
+  <si>
+    <t>4121</t>
+  </si>
+  <si>
+    <t>4122</t>
+  </si>
+  <si>
+    <t>4123</t>
+  </si>
+  <si>
+    <t>4124</t>
+  </si>
+  <si>
+    <t>4126</t>
+  </si>
+  <si>
+    <t>4127</t>
+  </si>
+  <si>
+    <t>4128</t>
+  </si>
+  <si>
+    <t>4129</t>
+  </si>
+  <si>
+    <t>4130</t>
+  </si>
+  <si>
+    <t>4131</t>
+  </si>
+  <si>
+    <t>4132</t>
+  </si>
+  <si>
+    <t>4133</t>
+  </si>
+  <si>
+    <t>4134</t>
+  </si>
+  <si>
+    <t>4135</t>
+  </si>
+  <si>
+    <t>4137</t>
+  </si>
+  <si>
+    <t>4138</t>
+  </si>
+  <si>
+    <t>4140</t>
+  </si>
+  <si>
+    <t>4142</t>
+  </si>
+  <si>
+    <t>4143</t>
+  </si>
+  <si>
+    <t>4144</t>
+  </si>
+  <si>
+    <t>5101</t>
+  </si>
+  <si>
+    <t>5103</t>
+  </si>
+  <si>
+    <t>5104</t>
+  </si>
+  <si>
+    <t>5107</t>
+  </si>
+  <si>
+    <t>5108</t>
+  </si>
+  <si>
+    <t>5109</t>
+  </si>
+  <si>
+    <t>5110</t>
+  </si>
+  <si>
+    <t>5111</t>
+  </si>
+  <si>
+    <t>5112</t>
+  </si>
+  <si>
+    <t>5114</t>
+  </si>
+  <si>
+    <t>5115</t>
+  </si>
+  <si>
+    <t>5116</t>
+  </si>
+  <si>
+    <t>5117</t>
+  </si>
+  <si>
+    <t>5120</t>
+  </si>
+  <si>
+    <t>5121</t>
+  </si>
+  <si>
+    <t>5122</t>
+  </si>
+  <si>
+    <t>5124</t>
+  </si>
+  <si>
+    <t>5126</t>
+  </si>
+  <si>
+    <t>5127</t>
+  </si>
+  <si>
+    <t>5128</t>
+  </si>
+  <si>
+    <t>5129</t>
+  </si>
+  <si>
+    <t>5130</t>
+  </si>
+  <si>
+    <t>5134</t>
+  </si>
+  <si>
+    <t>5135</t>
+  </si>
+  <si>
+    <t>5140</t>
+  </si>
+  <si>
+    <t>5141</t>
+  </si>
+  <si>
+    <t>5143</t>
+  </si>
+  <si>
+    <t>5218</t>
+  </si>
+  <si>
+    <t>Konferenzr.</t>
+  </si>
+  <si>
+    <t>5219</t>
+  </si>
+  <si>
+    <t>6112</t>
+  </si>
+  <si>
+    <t>6113</t>
+  </si>
+  <si>
+    <t>6114</t>
+  </si>
+  <si>
+    <t>6116</t>
+  </si>
+  <si>
+    <t>6117</t>
+  </si>
+  <si>
+    <t>6118</t>
+  </si>
+  <si>
+    <t>6120</t>
+  </si>
+  <si>
+    <t>6122</t>
+  </si>
+  <si>
+    <t>6126</t>
+  </si>
+  <si>
+    <t>6128</t>
+  </si>
+  <si>
+    <t>6131</t>
+  </si>
+  <si>
+    <t>6132</t>
+  </si>
+  <si>
+    <t>6133</t>
+  </si>
+  <si>
+    <t>6135</t>
+  </si>
+  <si>
+    <t>6138</t>
+  </si>
+  <si>
+    <t>6140</t>
+  </si>
+  <si>
+    <t>6141</t>
+  </si>
+  <si>
+    <t>6142</t>
+  </si>
+  <si>
+    <t>6143</t>
+  </si>
+  <si>
+    <t>6144</t>
+  </si>
+  <si>
+    <t>6203</t>
+  </si>
+  <si>
+    <t>6204</t>
+  </si>
+  <si>
+    <t>6205</t>
+  </si>
+  <si>
+    <t>6206</t>
+  </si>
+  <si>
+    <t>6207</t>
+  </si>
+  <si>
+    <t>6208</t>
+  </si>
+  <si>
+    <t>OG 7</t>
+  </si>
+  <si>
+    <t>7101</t>
+  </si>
+  <si>
+    <t>7103</t>
+  </si>
+  <si>
+    <t>7104</t>
+  </si>
+  <si>
+    <t>7105</t>
+  </si>
+  <si>
+    <t>7106</t>
+  </si>
+  <si>
+    <t>7108</t>
+  </si>
+  <si>
+    <t>7109</t>
+  </si>
+  <si>
+    <t>7111</t>
+  </si>
+  <si>
+    <t>7112</t>
+  </si>
+  <si>
+    <t>7113</t>
+  </si>
+  <si>
+    <t>7115</t>
+  </si>
+  <si>
+    <t>7117</t>
+  </si>
+  <si>
+    <t>7119</t>
+  </si>
+  <si>
+    <t>7120</t>
+  </si>
+  <si>
+    <t>7122</t>
+  </si>
+  <si>
+    <t>7123</t>
+  </si>
+  <si>
+    <t>7124</t>
+  </si>
+  <si>
+    <t>7126</t>
+  </si>
+  <si>
+    <t>7214</t>
+  </si>
+  <si>
+    <t>7215</t>
+  </si>
+  <si>
+    <t>7216</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;m²&quot;"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2881,13 +4271,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2899,14 +4313,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 4 2" xfId="1" xr:uid="{943AF215-5B10-4B57-84D4-04BE18A57413}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2919,6 +4354,186 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="&gt;&gt; GA &gt;&gt;"/>
+      <sheetName val="Tabellen"/>
+      <sheetName val="GA_Zusammenfassung"/>
+      <sheetName val="Baseline"/>
+      <sheetName val="Stromlastgang"/>
+      <sheetName val="GA_Pumpen"/>
+      <sheetName val="GA_RLT_MSR"/>
+      <sheetName val="GA_PV"/>
+      <sheetName val="GA_Zählerstände"/>
+      <sheetName val="GA_Beleuchtung_Standard"/>
+      <sheetName val="GA_Beleuchtung_VDI3807"/>
+      <sheetName val="Raumflächenverzeichnis"/>
+      <sheetName val="Beleuchtungsliste_Ausschreibung"/>
+      <sheetName val="Bürogröße"/>
+      <sheetName val="Treppenhäuser"/>
+      <sheetName val="WC"/>
+      <sheetName val="Lage"/>
+      <sheetName val="&gt;&gt; FA &gt;&gt;"/>
+      <sheetName val="Zusammenfassung"/>
+      <sheetName val="Zusammenstellung LM"/>
+      <sheetName val="Heizkurven"/>
+      <sheetName val="Temperaturvorgaben"/>
+      <sheetName val="Beleuchtung_Marsing"/>
+      <sheetName val="Beleuchtung"/>
+      <sheetName val="Beleuchtung_WC"/>
+      <sheetName val="Beleuchtung_raumweise"/>
+      <sheetName val="VDI 3807-4"/>
+      <sheetName val="Pumpen"/>
+      <sheetName val="RLT"/>
+      <sheetName val="RLT Gebhardt"/>
+      <sheetName val="MSR"/>
+      <sheetName val="Energierechnungen"/>
+      <sheetName val="Sonstiges"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="40">
+          <cell r="B40">
+            <v>0.14866000000000001</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42">
+            <v>85.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="&gt;&gt; GA &gt;&gt;"/>
+      <sheetName val="Tabellen"/>
+      <sheetName val="GA_Zusammenfassung"/>
+      <sheetName val="Baseline"/>
+      <sheetName val="Stromlastgang"/>
+      <sheetName val="GA_Pumpen"/>
+      <sheetName val="GA_RLT_MSR"/>
+      <sheetName val="GA_PV"/>
+      <sheetName val="GA_Zählerstände"/>
+      <sheetName val="GA_Beleuchtung_Standard"/>
+      <sheetName val="GA_Beleuchtung_VDI3807"/>
+      <sheetName val="Raumflächenverzeichnis"/>
+      <sheetName val="Beleuchtungsliste_Ausschreibung"/>
+      <sheetName val="Bürogröße"/>
+      <sheetName val="Treppenhäuser"/>
+      <sheetName val="WC"/>
+      <sheetName val="Lage"/>
+      <sheetName val="&gt;&gt; FA &gt;&gt;"/>
+      <sheetName val="Zusammenfassung"/>
+      <sheetName val="Zusammenstellung LM"/>
+      <sheetName val="Heizkurven"/>
+      <sheetName val="Temperaturvorgaben"/>
+      <sheetName val="Beleuchtung_Marsing"/>
+      <sheetName val="Beleuchtung"/>
+      <sheetName val="Beleuchtung_WC"/>
+      <sheetName val="Beleuchtung_raumweise"/>
+      <sheetName val="VDI 3807-4"/>
+      <sheetName val="Pumpen"/>
+      <sheetName val="Raumflächenverzeichnis mit HK"/>
+      <sheetName val="Auswertung"/>
+      <sheetName val="RLT"/>
+      <sheetName val="RLT Gebhardt"/>
+      <sheetName val="MSR"/>
+      <sheetName val="Energierechnungen"/>
+      <sheetName val="Sonstiges"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="40">
+          <cell r="B40">
+            <v>0.14866000000000001</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42">
+            <v>85.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3205,6 +4820,4690 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA88C93-584A-45FC-963A-8A6764F621B2}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E302"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="5" customWidth="1"/>
+    <col min="5" max="240" width="9.140625" style="2"/>
+    <col min="241" max="241" width="9.42578125" style="2" customWidth="1"/>
+    <col min="242" max="242" width="13" style="2" customWidth="1"/>
+    <col min="243" max="243" width="21.28515625" style="2" customWidth="1"/>
+    <col min="244" max="244" width="13.42578125" style="2" customWidth="1"/>
+    <col min="245" max="245" width="14" style="2" customWidth="1"/>
+    <col min="246" max="246" width="11.42578125" style="2" customWidth="1"/>
+    <col min="247" max="496" width="9.140625" style="2"/>
+    <col min="497" max="497" width="9.42578125" style="2" customWidth="1"/>
+    <col min="498" max="498" width="13" style="2" customWidth="1"/>
+    <col min="499" max="499" width="21.28515625" style="2" customWidth="1"/>
+    <col min="500" max="500" width="13.42578125" style="2" customWidth="1"/>
+    <col min="501" max="501" width="14" style="2" customWidth="1"/>
+    <col min="502" max="502" width="11.42578125" style="2" customWidth="1"/>
+    <col min="503" max="752" width="9.140625" style="2"/>
+    <col min="753" max="753" width="9.42578125" style="2" customWidth="1"/>
+    <col min="754" max="754" width="13" style="2" customWidth="1"/>
+    <col min="755" max="755" width="21.28515625" style="2" customWidth="1"/>
+    <col min="756" max="756" width="13.42578125" style="2" customWidth="1"/>
+    <col min="757" max="757" width="14" style="2" customWidth="1"/>
+    <col min="758" max="758" width="11.42578125" style="2" customWidth="1"/>
+    <col min="759" max="1008" width="9.140625" style="2"/>
+    <col min="1009" max="1009" width="9.42578125" style="2" customWidth="1"/>
+    <col min="1010" max="1010" width="13" style="2" customWidth="1"/>
+    <col min="1011" max="1011" width="21.28515625" style="2" customWidth="1"/>
+    <col min="1012" max="1012" width="13.42578125" style="2" customWidth="1"/>
+    <col min="1013" max="1013" width="14" style="2" customWidth="1"/>
+    <col min="1014" max="1014" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1015" max="1264" width="9.140625" style="2"/>
+    <col min="1265" max="1265" width="9.42578125" style="2" customWidth="1"/>
+    <col min="1266" max="1266" width="13" style="2" customWidth="1"/>
+    <col min="1267" max="1267" width="21.28515625" style="2" customWidth="1"/>
+    <col min="1268" max="1268" width="13.42578125" style="2" customWidth="1"/>
+    <col min="1269" max="1269" width="14" style="2" customWidth="1"/>
+    <col min="1270" max="1270" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1271" max="1520" width="9.140625" style="2"/>
+    <col min="1521" max="1521" width="9.42578125" style="2" customWidth="1"/>
+    <col min="1522" max="1522" width="13" style="2" customWidth="1"/>
+    <col min="1523" max="1523" width="21.28515625" style="2" customWidth="1"/>
+    <col min="1524" max="1524" width="13.42578125" style="2" customWidth="1"/>
+    <col min="1525" max="1525" width="14" style="2" customWidth="1"/>
+    <col min="1526" max="1526" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1527" max="1776" width="9.140625" style="2"/>
+    <col min="1777" max="1777" width="9.42578125" style="2" customWidth="1"/>
+    <col min="1778" max="1778" width="13" style="2" customWidth="1"/>
+    <col min="1779" max="1779" width="21.28515625" style="2" customWidth="1"/>
+    <col min="1780" max="1780" width="13.42578125" style="2" customWidth="1"/>
+    <col min="1781" max="1781" width="14" style="2" customWidth="1"/>
+    <col min="1782" max="1782" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1783" max="2032" width="9.140625" style="2"/>
+    <col min="2033" max="2033" width="9.42578125" style="2" customWidth="1"/>
+    <col min="2034" max="2034" width="13" style="2" customWidth="1"/>
+    <col min="2035" max="2035" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2036" max="2036" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2037" max="2037" width="14" style="2" customWidth="1"/>
+    <col min="2038" max="2038" width="11.42578125" style="2" customWidth="1"/>
+    <col min="2039" max="2288" width="9.140625" style="2"/>
+    <col min="2289" max="2289" width="9.42578125" style="2" customWidth="1"/>
+    <col min="2290" max="2290" width="13" style="2" customWidth="1"/>
+    <col min="2291" max="2291" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2292" max="2292" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2293" max="2293" width="14" style="2" customWidth="1"/>
+    <col min="2294" max="2294" width="11.42578125" style="2" customWidth="1"/>
+    <col min="2295" max="2544" width="9.140625" style="2"/>
+    <col min="2545" max="2545" width="9.42578125" style="2" customWidth="1"/>
+    <col min="2546" max="2546" width="13" style="2" customWidth="1"/>
+    <col min="2547" max="2547" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2548" max="2548" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2549" max="2549" width="14" style="2" customWidth="1"/>
+    <col min="2550" max="2550" width="11.42578125" style="2" customWidth="1"/>
+    <col min="2551" max="2800" width="9.140625" style="2"/>
+    <col min="2801" max="2801" width="9.42578125" style="2" customWidth="1"/>
+    <col min="2802" max="2802" width="13" style="2" customWidth="1"/>
+    <col min="2803" max="2803" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2804" max="2804" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2805" max="2805" width="14" style="2" customWidth="1"/>
+    <col min="2806" max="2806" width="11.42578125" style="2" customWidth="1"/>
+    <col min="2807" max="3056" width="9.140625" style="2"/>
+    <col min="3057" max="3057" width="9.42578125" style="2" customWidth="1"/>
+    <col min="3058" max="3058" width="13" style="2" customWidth="1"/>
+    <col min="3059" max="3059" width="21.28515625" style="2" customWidth="1"/>
+    <col min="3060" max="3060" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3061" max="3061" width="14" style="2" customWidth="1"/>
+    <col min="3062" max="3062" width="11.42578125" style="2" customWidth="1"/>
+    <col min="3063" max="3312" width="9.140625" style="2"/>
+    <col min="3313" max="3313" width="9.42578125" style="2" customWidth="1"/>
+    <col min="3314" max="3314" width="13" style="2" customWidth="1"/>
+    <col min="3315" max="3315" width="21.28515625" style="2" customWidth="1"/>
+    <col min="3316" max="3316" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3317" max="3317" width="14" style="2" customWidth="1"/>
+    <col min="3318" max="3318" width="11.42578125" style="2" customWidth="1"/>
+    <col min="3319" max="3568" width="9.140625" style="2"/>
+    <col min="3569" max="3569" width="9.42578125" style="2" customWidth="1"/>
+    <col min="3570" max="3570" width="13" style="2" customWidth="1"/>
+    <col min="3571" max="3571" width="21.28515625" style="2" customWidth="1"/>
+    <col min="3572" max="3572" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3573" max="3573" width="14" style="2" customWidth="1"/>
+    <col min="3574" max="3574" width="11.42578125" style="2" customWidth="1"/>
+    <col min="3575" max="3824" width="9.140625" style="2"/>
+    <col min="3825" max="3825" width="9.42578125" style="2" customWidth="1"/>
+    <col min="3826" max="3826" width="13" style="2" customWidth="1"/>
+    <col min="3827" max="3827" width="21.28515625" style="2" customWidth="1"/>
+    <col min="3828" max="3828" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3829" max="3829" width="14" style="2" customWidth="1"/>
+    <col min="3830" max="3830" width="11.42578125" style="2" customWidth="1"/>
+    <col min="3831" max="4080" width="9.140625" style="2"/>
+    <col min="4081" max="4081" width="9.42578125" style="2" customWidth="1"/>
+    <col min="4082" max="4082" width="13" style="2" customWidth="1"/>
+    <col min="4083" max="4083" width="21.28515625" style="2" customWidth="1"/>
+    <col min="4084" max="4084" width="13.42578125" style="2" customWidth="1"/>
+    <col min="4085" max="4085" width="14" style="2" customWidth="1"/>
+    <col min="4086" max="4086" width="11.42578125" style="2" customWidth="1"/>
+    <col min="4087" max="4336" width="9.140625" style="2"/>
+    <col min="4337" max="4337" width="9.42578125" style="2" customWidth="1"/>
+    <col min="4338" max="4338" width="13" style="2" customWidth="1"/>
+    <col min="4339" max="4339" width="21.28515625" style="2" customWidth="1"/>
+    <col min="4340" max="4340" width="13.42578125" style="2" customWidth="1"/>
+    <col min="4341" max="4341" width="14" style="2" customWidth="1"/>
+    <col min="4342" max="4342" width="11.42578125" style="2" customWidth="1"/>
+    <col min="4343" max="4592" width="9.140625" style="2"/>
+    <col min="4593" max="4593" width="9.42578125" style="2" customWidth="1"/>
+    <col min="4594" max="4594" width="13" style="2" customWidth="1"/>
+    <col min="4595" max="4595" width="21.28515625" style="2" customWidth="1"/>
+    <col min="4596" max="4596" width="13.42578125" style="2" customWidth="1"/>
+    <col min="4597" max="4597" width="14" style="2" customWidth="1"/>
+    <col min="4598" max="4598" width="11.42578125" style="2" customWidth="1"/>
+    <col min="4599" max="4848" width="9.140625" style="2"/>
+    <col min="4849" max="4849" width="9.42578125" style="2" customWidth="1"/>
+    <col min="4850" max="4850" width="13" style="2" customWidth="1"/>
+    <col min="4851" max="4851" width="21.28515625" style="2" customWidth="1"/>
+    <col min="4852" max="4852" width="13.42578125" style="2" customWidth="1"/>
+    <col min="4853" max="4853" width="14" style="2" customWidth="1"/>
+    <col min="4854" max="4854" width="11.42578125" style="2" customWidth="1"/>
+    <col min="4855" max="5104" width="9.140625" style="2"/>
+    <col min="5105" max="5105" width="9.42578125" style="2" customWidth="1"/>
+    <col min="5106" max="5106" width="13" style="2" customWidth="1"/>
+    <col min="5107" max="5107" width="21.28515625" style="2" customWidth="1"/>
+    <col min="5108" max="5108" width="13.42578125" style="2" customWidth="1"/>
+    <col min="5109" max="5109" width="14" style="2" customWidth="1"/>
+    <col min="5110" max="5110" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5111" max="5360" width="9.140625" style="2"/>
+    <col min="5361" max="5361" width="9.42578125" style="2" customWidth="1"/>
+    <col min="5362" max="5362" width="13" style="2" customWidth="1"/>
+    <col min="5363" max="5363" width="21.28515625" style="2" customWidth="1"/>
+    <col min="5364" max="5364" width="13.42578125" style="2" customWidth="1"/>
+    <col min="5365" max="5365" width="14" style="2" customWidth="1"/>
+    <col min="5366" max="5366" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5367" max="5616" width="9.140625" style="2"/>
+    <col min="5617" max="5617" width="9.42578125" style="2" customWidth="1"/>
+    <col min="5618" max="5618" width="13" style="2" customWidth="1"/>
+    <col min="5619" max="5619" width="21.28515625" style="2" customWidth="1"/>
+    <col min="5620" max="5620" width="13.42578125" style="2" customWidth="1"/>
+    <col min="5621" max="5621" width="14" style="2" customWidth="1"/>
+    <col min="5622" max="5622" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5623" max="5872" width="9.140625" style="2"/>
+    <col min="5873" max="5873" width="9.42578125" style="2" customWidth="1"/>
+    <col min="5874" max="5874" width="13" style="2" customWidth="1"/>
+    <col min="5875" max="5875" width="21.28515625" style="2" customWidth="1"/>
+    <col min="5876" max="5876" width="13.42578125" style="2" customWidth="1"/>
+    <col min="5877" max="5877" width="14" style="2" customWidth="1"/>
+    <col min="5878" max="5878" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5879" max="6128" width="9.140625" style="2"/>
+    <col min="6129" max="6129" width="9.42578125" style="2" customWidth="1"/>
+    <col min="6130" max="6130" width="13" style="2" customWidth="1"/>
+    <col min="6131" max="6131" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6132" max="6132" width="13.42578125" style="2" customWidth="1"/>
+    <col min="6133" max="6133" width="14" style="2" customWidth="1"/>
+    <col min="6134" max="6134" width="11.42578125" style="2" customWidth="1"/>
+    <col min="6135" max="6384" width="9.140625" style="2"/>
+    <col min="6385" max="6385" width="9.42578125" style="2" customWidth="1"/>
+    <col min="6386" max="6386" width="13" style="2" customWidth="1"/>
+    <col min="6387" max="6387" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6388" max="6388" width="13.42578125" style="2" customWidth="1"/>
+    <col min="6389" max="6389" width="14" style="2" customWidth="1"/>
+    <col min="6390" max="6390" width="11.42578125" style="2" customWidth="1"/>
+    <col min="6391" max="6640" width="9.140625" style="2"/>
+    <col min="6641" max="6641" width="9.42578125" style="2" customWidth="1"/>
+    <col min="6642" max="6642" width="13" style="2" customWidth="1"/>
+    <col min="6643" max="6643" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6644" max="6644" width="13.42578125" style="2" customWidth="1"/>
+    <col min="6645" max="6645" width="14" style="2" customWidth="1"/>
+    <col min="6646" max="6646" width="11.42578125" style="2" customWidth="1"/>
+    <col min="6647" max="6896" width="9.140625" style="2"/>
+    <col min="6897" max="6897" width="9.42578125" style="2" customWidth="1"/>
+    <col min="6898" max="6898" width="13" style="2" customWidth="1"/>
+    <col min="6899" max="6899" width="21.28515625" style="2" customWidth="1"/>
+    <col min="6900" max="6900" width="13.42578125" style="2" customWidth="1"/>
+    <col min="6901" max="6901" width="14" style="2" customWidth="1"/>
+    <col min="6902" max="6902" width="11.42578125" style="2" customWidth="1"/>
+    <col min="6903" max="7152" width="9.140625" style="2"/>
+    <col min="7153" max="7153" width="9.42578125" style="2" customWidth="1"/>
+    <col min="7154" max="7154" width="13" style="2" customWidth="1"/>
+    <col min="7155" max="7155" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7156" max="7156" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7157" max="7157" width="14" style="2" customWidth="1"/>
+    <col min="7158" max="7158" width="11.42578125" style="2" customWidth="1"/>
+    <col min="7159" max="7408" width="9.140625" style="2"/>
+    <col min="7409" max="7409" width="9.42578125" style="2" customWidth="1"/>
+    <col min="7410" max="7410" width="13" style="2" customWidth="1"/>
+    <col min="7411" max="7411" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7412" max="7412" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7413" max="7413" width="14" style="2" customWidth="1"/>
+    <col min="7414" max="7414" width="11.42578125" style="2" customWidth="1"/>
+    <col min="7415" max="7664" width="9.140625" style="2"/>
+    <col min="7665" max="7665" width="9.42578125" style="2" customWidth="1"/>
+    <col min="7666" max="7666" width="13" style="2" customWidth="1"/>
+    <col min="7667" max="7667" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7668" max="7668" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7669" max="7669" width="14" style="2" customWidth="1"/>
+    <col min="7670" max="7670" width="11.42578125" style="2" customWidth="1"/>
+    <col min="7671" max="7920" width="9.140625" style="2"/>
+    <col min="7921" max="7921" width="9.42578125" style="2" customWidth="1"/>
+    <col min="7922" max="7922" width="13" style="2" customWidth="1"/>
+    <col min="7923" max="7923" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7924" max="7924" width="13.42578125" style="2" customWidth="1"/>
+    <col min="7925" max="7925" width="14" style="2" customWidth="1"/>
+    <col min="7926" max="7926" width="11.42578125" style="2" customWidth="1"/>
+    <col min="7927" max="8176" width="9.140625" style="2"/>
+    <col min="8177" max="8177" width="9.42578125" style="2" customWidth="1"/>
+    <col min="8178" max="8178" width="13" style="2" customWidth="1"/>
+    <col min="8179" max="8179" width="21.28515625" style="2" customWidth="1"/>
+    <col min="8180" max="8180" width="13.42578125" style="2" customWidth="1"/>
+    <col min="8181" max="8181" width="14" style="2" customWidth="1"/>
+    <col min="8182" max="8182" width="11.42578125" style="2" customWidth="1"/>
+    <col min="8183" max="8432" width="9.140625" style="2"/>
+    <col min="8433" max="8433" width="9.42578125" style="2" customWidth="1"/>
+    <col min="8434" max="8434" width="13" style="2" customWidth="1"/>
+    <col min="8435" max="8435" width="21.28515625" style="2" customWidth="1"/>
+    <col min="8436" max="8436" width="13.42578125" style="2" customWidth="1"/>
+    <col min="8437" max="8437" width="14" style="2" customWidth="1"/>
+    <col min="8438" max="8438" width="11.42578125" style="2" customWidth="1"/>
+    <col min="8439" max="8688" width="9.140625" style="2"/>
+    <col min="8689" max="8689" width="9.42578125" style="2" customWidth="1"/>
+    <col min="8690" max="8690" width="13" style="2" customWidth="1"/>
+    <col min="8691" max="8691" width="21.28515625" style="2" customWidth="1"/>
+    <col min="8692" max="8692" width="13.42578125" style="2" customWidth="1"/>
+    <col min="8693" max="8693" width="14" style="2" customWidth="1"/>
+    <col min="8694" max="8694" width="11.42578125" style="2" customWidth="1"/>
+    <col min="8695" max="8944" width="9.140625" style="2"/>
+    <col min="8945" max="8945" width="9.42578125" style="2" customWidth="1"/>
+    <col min="8946" max="8946" width="13" style="2" customWidth="1"/>
+    <col min="8947" max="8947" width="21.28515625" style="2" customWidth="1"/>
+    <col min="8948" max="8948" width="13.42578125" style="2" customWidth="1"/>
+    <col min="8949" max="8949" width="14" style="2" customWidth="1"/>
+    <col min="8950" max="8950" width="11.42578125" style="2" customWidth="1"/>
+    <col min="8951" max="9200" width="9.140625" style="2"/>
+    <col min="9201" max="9201" width="9.42578125" style="2" customWidth="1"/>
+    <col min="9202" max="9202" width="13" style="2" customWidth="1"/>
+    <col min="9203" max="9203" width="21.28515625" style="2" customWidth="1"/>
+    <col min="9204" max="9204" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9205" max="9205" width="14" style="2" customWidth="1"/>
+    <col min="9206" max="9206" width="11.42578125" style="2" customWidth="1"/>
+    <col min="9207" max="9456" width="9.140625" style="2"/>
+    <col min="9457" max="9457" width="9.42578125" style="2" customWidth="1"/>
+    <col min="9458" max="9458" width="13" style="2" customWidth="1"/>
+    <col min="9459" max="9459" width="21.28515625" style="2" customWidth="1"/>
+    <col min="9460" max="9460" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9461" max="9461" width="14" style="2" customWidth="1"/>
+    <col min="9462" max="9462" width="11.42578125" style="2" customWidth="1"/>
+    <col min="9463" max="9712" width="9.140625" style="2"/>
+    <col min="9713" max="9713" width="9.42578125" style="2" customWidth="1"/>
+    <col min="9714" max="9714" width="13" style="2" customWidth="1"/>
+    <col min="9715" max="9715" width="21.28515625" style="2" customWidth="1"/>
+    <col min="9716" max="9716" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9717" max="9717" width="14" style="2" customWidth="1"/>
+    <col min="9718" max="9718" width="11.42578125" style="2" customWidth="1"/>
+    <col min="9719" max="9968" width="9.140625" style="2"/>
+    <col min="9969" max="9969" width="9.42578125" style="2" customWidth="1"/>
+    <col min="9970" max="9970" width="13" style="2" customWidth="1"/>
+    <col min="9971" max="9971" width="21.28515625" style="2" customWidth="1"/>
+    <col min="9972" max="9972" width="13.42578125" style="2" customWidth="1"/>
+    <col min="9973" max="9973" width="14" style="2" customWidth="1"/>
+    <col min="9974" max="9974" width="11.42578125" style="2" customWidth="1"/>
+    <col min="9975" max="10224" width="9.140625" style="2"/>
+    <col min="10225" max="10225" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10226" max="10226" width="13" style="2" customWidth="1"/>
+    <col min="10227" max="10227" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10228" max="10228" width="13.42578125" style="2" customWidth="1"/>
+    <col min="10229" max="10229" width="14" style="2" customWidth="1"/>
+    <col min="10230" max="10230" width="11.42578125" style="2" customWidth="1"/>
+    <col min="10231" max="10480" width="9.140625" style="2"/>
+    <col min="10481" max="10481" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10482" max="10482" width="13" style="2" customWidth="1"/>
+    <col min="10483" max="10483" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10484" max="10484" width="13.42578125" style="2" customWidth="1"/>
+    <col min="10485" max="10485" width="14" style="2" customWidth="1"/>
+    <col min="10486" max="10486" width="11.42578125" style="2" customWidth="1"/>
+    <col min="10487" max="10736" width="9.140625" style="2"/>
+    <col min="10737" max="10737" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10738" max="10738" width="13" style="2" customWidth="1"/>
+    <col min="10739" max="10739" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10740" max="10740" width="13.42578125" style="2" customWidth="1"/>
+    <col min="10741" max="10741" width="14" style="2" customWidth="1"/>
+    <col min="10742" max="10742" width="11.42578125" style="2" customWidth="1"/>
+    <col min="10743" max="10992" width="9.140625" style="2"/>
+    <col min="10993" max="10993" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10994" max="10994" width="13" style="2" customWidth="1"/>
+    <col min="10995" max="10995" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10996" max="10996" width="13.42578125" style="2" customWidth="1"/>
+    <col min="10997" max="10997" width="14" style="2" customWidth="1"/>
+    <col min="10998" max="10998" width="11.42578125" style="2" customWidth="1"/>
+    <col min="10999" max="11248" width="9.140625" style="2"/>
+    <col min="11249" max="11249" width="9.42578125" style="2" customWidth="1"/>
+    <col min="11250" max="11250" width="13" style="2" customWidth="1"/>
+    <col min="11251" max="11251" width="21.28515625" style="2" customWidth="1"/>
+    <col min="11252" max="11252" width="13.42578125" style="2" customWidth="1"/>
+    <col min="11253" max="11253" width="14" style="2" customWidth="1"/>
+    <col min="11254" max="11254" width="11.42578125" style="2" customWidth="1"/>
+    <col min="11255" max="11504" width="9.140625" style="2"/>
+    <col min="11505" max="11505" width="9.42578125" style="2" customWidth="1"/>
+    <col min="11506" max="11506" width="13" style="2" customWidth="1"/>
+    <col min="11507" max="11507" width="21.28515625" style="2" customWidth="1"/>
+    <col min="11508" max="11508" width="13.42578125" style="2" customWidth="1"/>
+    <col min="11509" max="11509" width="14" style="2" customWidth="1"/>
+    <col min="11510" max="11510" width="11.42578125" style="2" customWidth="1"/>
+    <col min="11511" max="11760" width="9.140625" style="2"/>
+    <col min="11761" max="11761" width="9.42578125" style="2" customWidth="1"/>
+    <col min="11762" max="11762" width="13" style="2" customWidth="1"/>
+    <col min="11763" max="11763" width="21.28515625" style="2" customWidth="1"/>
+    <col min="11764" max="11764" width="13.42578125" style="2" customWidth="1"/>
+    <col min="11765" max="11765" width="14" style="2" customWidth="1"/>
+    <col min="11766" max="11766" width="11.42578125" style="2" customWidth="1"/>
+    <col min="11767" max="12016" width="9.140625" style="2"/>
+    <col min="12017" max="12017" width="9.42578125" style="2" customWidth="1"/>
+    <col min="12018" max="12018" width="13" style="2" customWidth="1"/>
+    <col min="12019" max="12019" width="21.28515625" style="2" customWidth="1"/>
+    <col min="12020" max="12020" width="13.42578125" style="2" customWidth="1"/>
+    <col min="12021" max="12021" width="14" style="2" customWidth="1"/>
+    <col min="12022" max="12022" width="11.42578125" style="2" customWidth="1"/>
+    <col min="12023" max="12272" width="9.140625" style="2"/>
+    <col min="12273" max="12273" width="9.42578125" style="2" customWidth="1"/>
+    <col min="12274" max="12274" width="13" style="2" customWidth="1"/>
+    <col min="12275" max="12275" width="21.28515625" style="2" customWidth="1"/>
+    <col min="12276" max="12276" width="13.42578125" style="2" customWidth="1"/>
+    <col min="12277" max="12277" width="14" style="2" customWidth="1"/>
+    <col min="12278" max="12278" width="11.42578125" style="2" customWidth="1"/>
+    <col min="12279" max="12528" width="9.140625" style="2"/>
+    <col min="12529" max="12529" width="9.42578125" style="2" customWidth="1"/>
+    <col min="12530" max="12530" width="13" style="2" customWidth="1"/>
+    <col min="12531" max="12531" width="21.28515625" style="2" customWidth="1"/>
+    <col min="12532" max="12532" width="13.42578125" style="2" customWidth="1"/>
+    <col min="12533" max="12533" width="14" style="2" customWidth="1"/>
+    <col min="12534" max="12534" width="11.42578125" style="2" customWidth="1"/>
+    <col min="12535" max="12784" width="9.140625" style="2"/>
+    <col min="12785" max="12785" width="9.42578125" style="2" customWidth="1"/>
+    <col min="12786" max="12786" width="13" style="2" customWidth="1"/>
+    <col min="12787" max="12787" width="21.28515625" style="2" customWidth="1"/>
+    <col min="12788" max="12788" width="13.42578125" style="2" customWidth="1"/>
+    <col min="12789" max="12789" width="14" style="2" customWidth="1"/>
+    <col min="12790" max="12790" width="11.42578125" style="2" customWidth="1"/>
+    <col min="12791" max="13040" width="9.140625" style="2"/>
+    <col min="13041" max="13041" width="9.42578125" style="2" customWidth="1"/>
+    <col min="13042" max="13042" width="13" style="2" customWidth="1"/>
+    <col min="13043" max="13043" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13044" max="13044" width="13.42578125" style="2" customWidth="1"/>
+    <col min="13045" max="13045" width="14" style="2" customWidth="1"/>
+    <col min="13046" max="13046" width="11.42578125" style="2" customWidth="1"/>
+    <col min="13047" max="13296" width="9.140625" style="2"/>
+    <col min="13297" max="13297" width="9.42578125" style="2" customWidth="1"/>
+    <col min="13298" max="13298" width="13" style="2" customWidth="1"/>
+    <col min="13299" max="13299" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13300" max="13300" width="13.42578125" style="2" customWidth="1"/>
+    <col min="13301" max="13301" width="14" style="2" customWidth="1"/>
+    <col min="13302" max="13302" width="11.42578125" style="2" customWidth="1"/>
+    <col min="13303" max="13552" width="9.140625" style="2"/>
+    <col min="13553" max="13553" width="9.42578125" style="2" customWidth="1"/>
+    <col min="13554" max="13554" width="13" style="2" customWidth="1"/>
+    <col min="13555" max="13555" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13556" max="13556" width="13.42578125" style="2" customWidth="1"/>
+    <col min="13557" max="13557" width="14" style="2" customWidth="1"/>
+    <col min="13558" max="13558" width="11.42578125" style="2" customWidth="1"/>
+    <col min="13559" max="13808" width="9.140625" style="2"/>
+    <col min="13809" max="13809" width="9.42578125" style="2" customWidth="1"/>
+    <col min="13810" max="13810" width="13" style="2" customWidth="1"/>
+    <col min="13811" max="13811" width="21.28515625" style="2" customWidth="1"/>
+    <col min="13812" max="13812" width="13.42578125" style="2" customWidth="1"/>
+    <col min="13813" max="13813" width="14" style="2" customWidth="1"/>
+    <col min="13814" max="13814" width="11.42578125" style="2" customWidth="1"/>
+    <col min="13815" max="14064" width="9.140625" style="2"/>
+    <col min="14065" max="14065" width="9.42578125" style="2" customWidth="1"/>
+    <col min="14066" max="14066" width="13" style="2" customWidth="1"/>
+    <col min="14067" max="14067" width="21.28515625" style="2" customWidth="1"/>
+    <col min="14068" max="14068" width="13.42578125" style="2" customWidth="1"/>
+    <col min="14069" max="14069" width="14" style="2" customWidth="1"/>
+    <col min="14070" max="14070" width="11.42578125" style="2" customWidth="1"/>
+    <col min="14071" max="14320" width="9.140625" style="2"/>
+    <col min="14321" max="14321" width="9.42578125" style="2" customWidth="1"/>
+    <col min="14322" max="14322" width="13" style="2" customWidth="1"/>
+    <col min="14323" max="14323" width="21.28515625" style="2" customWidth="1"/>
+    <col min="14324" max="14324" width="13.42578125" style="2" customWidth="1"/>
+    <col min="14325" max="14325" width="14" style="2" customWidth="1"/>
+    <col min="14326" max="14326" width="11.42578125" style="2" customWidth="1"/>
+    <col min="14327" max="14576" width="9.140625" style="2"/>
+    <col min="14577" max="14577" width="9.42578125" style="2" customWidth="1"/>
+    <col min="14578" max="14578" width="13" style="2" customWidth="1"/>
+    <col min="14579" max="14579" width="21.28515625" style="2" customWidth="1"/>
+    <col min="14580" max="14580" width="13.42578125" style="2" customWidth="1"/>
+    <col min="14581" max="14581" width="14" style="2" customWidth="1"/>
+    <col min="14582" max="14582" width="11.42578125" style="2" customWidth="1"/>
+    <col min="14583" max="14832" width="9.140625" style="2"/>
+    <col min="14833" max="14833" width="9.42578125" style="2" customWidth="1"/>
+    <col min="14834" max="14834" width="13" style="2" customWidth="1"/>
+    <col min="14835" max="14835" width="21.28515625" style="2" customWidth="1"/>
+    <col min="14836" max="14836" width="13.42578125" style="2" customWidth="1"/>
+    <col min="14837" max="14837" width="14" style="2" customWidth="1"/>
+    <col min="14838" max="14838" width="11.42578125" style="2" customWidth="1"/>
+    <col min="14839" max="15088" width="9.140625" style="2"/>
+    <col min="15089" max="15089" width="9.42578125" style="2" customWidth="1"/>
+    <col min="15090" max="15090" width="13" style="2" customWidth="1"/>
+    <col min="15091" max="15091" width="21.28515625" style="2" customWidth="1"/>
+    <col min="15092" max="15092" width="13.42578125" style="2" customWidth="1"/>
+    <col min="15093" max="15093" width="14" style="2" customWidth="1"/>
+    <col min="15094" max="15094" width="11.42578125" style="2" customWidth="1"/>
+    <col min="15095" max="15344" width="9.140625" style="2"/>
+    <col min="15345" max="15345" width="9.42578125" style="2" customWidth="1"/>
+    <col min="15346" max="15346" width="13" style="2" customWidth="1"/>
+    <col min="15347" max="15347" width="21.28515625" style="2" customWidth="1"/>
+    <col min="15348" max="15348" width="13.42578125" style="2" customWidth="1"/>
+    <col min="15349" max="15349" width="14" style="2" customWidth="1"/>
+    <col min="15350" max="15350" width="11.42578125" style="2" customWidth="1"/>
+    <col min="15351" max="15600" width="9.140625" style="2"/>
+    <col min="15601" max="15601" width="9.42578125" style="2" customWidth="1"/>
+    <col min="15602" max="15602" width="13" style="2" customWidth="1"/>
+    <col min="15603" max="15603" width="21.28515625" style="2" customWidth="1"/>
+    <col min="15604" max="15604" width="13.42578125" style="2" customWidth="1"/>
+    <col min="15605" max="15605" width="14" style="2" customWidth="1"/>
+    <col min="15606" max="15606" width="11.42578125" style="2" customWidth="1"/>
+    <col min="15607" max="15856" width="9.140625" style="2"/>
+    <col min="15857" max="15857" width="9.42578125" style="2" customWidth="1"/>
+    <col min="15858" max="15858" width="13" style="2" customWidth="1"/>
+    <col min="15859" max="15859" width="21.28515625" style="2" customWidth="1"/>
+    <col min="15860" max="15860" width="13.42578125" style="2" customWidth="1"/>
+    <col min="15861" max="15861" width="14" style="2" customWidth="1"/>
+    <col min="15862" max="15862" width="11.42578125" style="2" customWidth="1"/>
+    <col min="15863" max="16112" width="9.140625" style="2"/>
+    <col min="16113" max="16113" width="9.42578125" style="2" customWidth="1"/>
+    <col min="16114" max="16114" width="13" style="2" customWidth="1"/>
+    <col min="16115" max="16115" width="21.28515625" style="2" customWidth="1"/>
+    <col min="16116" max="16116" width="13.42578125" style="2" customWidth="1"/>
+    <col min="16117" max="16117" width="14" style="2" customWidth="1"/>
+    <col min="16118" max="16118" width="11.42578125" style="2" customWidth="1"/>
+    <col min="16119" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D2" s="4">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="D4" s="4">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>22.53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4">
+        <v>45.34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="4">
+        <v>24.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D9" s="4">
+        <v>24.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D10" s="4">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D11" s="4">
+        <v>24.73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D12" s="4">
+        <v>24.56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D14" s="4">
+        <v>24.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="D16" s="7">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D17" s="4">
+        <v>23.94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="D18" s="4">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D19" s="4">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D20" s="4">
+        <v>24.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="D22" s="4">
+        <v>9.0299999999999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="D23" s="4">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="D24" s="4">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D25" s="4">
+        <v>25.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D26" s="4">
+        <v>37.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="D27" s="4">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D28" s="4">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D29" s="4">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D30" s="4">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D31" s="4">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="4">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D33" s="4">
+        <v>22.04</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="D34" s="4">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D35" s="4">
+        <v>25.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="4">
+        <v>16.079999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D37" s="4">
+        <v>21.68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D38" s="4">
+        <v>16.760000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="4">
+        <v>13.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="4">
+        <v>19.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="4">
+        <v>18.440000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D42" s="4">
+        <v>52.34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="4">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="4">
+        <v>35.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="4">
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="4">
+        <v>25.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="4">
+        <v>19.14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="4">
+        <v>19.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="4">
+        <v>18.84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="4">
+        <v>17.93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="4">
+        <v>26.39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="4">
+        <v>25.27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D53" s="4">
+        <v>25.24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="4">
+        <v>24.41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="4">
+        <v>26.28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="4">
+        <v>11.66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="4">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D58" s="4">
+        <v>25.76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="4">
+        <v>38.340000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="4">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="4">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="4">
+        <v>15.96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D63" s="4">
+        <v>30.04</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="4">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="4">
+        <v>18.149999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="4">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D67" s="4">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="4">
+        <v>12.71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="4">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D70" s="4">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="4">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D72" s="4">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D73" s="4">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D74" s="4">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D75" s="4">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76" s="4">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="4">
+        <v>13.77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="4">
+        <v>47.57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="4">
+        <v>59.15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="4">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="4">
+        <v>17.05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="4">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="4">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="4">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="4">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" s="4">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="4">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="4">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D89" s="4">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D90" s="4">
+        <v>27.16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D91" s="4">
+        <v>17.79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D92" s="4">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D93" s="4">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D94" s="4">
+        <v>9.5299999999999994</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="4">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D96" s="4">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="4">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="4">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="4">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="4">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="4">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="4">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="4">
+        <v>25.44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D104" s="4">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="4">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="4">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D107" s="4">
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="4">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="4">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="4">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="4">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="4">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="4">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="4">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="4">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="4">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="4">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="4">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="4"/>
+    </row>
+    <row r="120" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D120" s="4">
+        <v>25.46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="4">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="4">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="4">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="4">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="4">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="4">
+        <v>22.24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="4">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="4">
+        <v>26.11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="4">
+        <v>12.93</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="4">
+        <v>12.87</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="4">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="4">
+        <v>15.53</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="4">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D134" s="4">
+        <v>10.96</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D135" s="4">
+        <v>74.12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D136" s="4">
+        <v>107.37</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D137" s="4">
+        <v>63.59</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D138" s="4">
+        <v>72.72</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D139" s="4">
+        <v>87.07</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D140" s="4">
+        <v>37.06</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="4">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D142" s="4">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D143" s="4">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D144" s="4">
+        <v>2.3199999999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="4">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="4">
+        <v>11.86</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="4">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="4">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="4">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="4">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D151" s="4">
+        <v>24.55</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="4">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="4">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="4">
+        <v>15.52</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="4">
+        <v>13.86</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="4">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="4">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="4">
+        <v>14.08</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" s="4">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="4">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="D161" s="4">
+        <v>10.039999999999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D162" s="4">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D163" s="4">
+        <v>22.51</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="4">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="4">
+        <v>21.76</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D166" s="4">
+        <v>28.96</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D167" s="4">
+        <v>21.16</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" s="4">
+        <v>25.24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="4">
+        <v>14.16</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="4">
+        <v>14.16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="4">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D172" s="4">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D173" s="4">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D174" s="4">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D175" s="4">
+        <v>78.88</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="4">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D177" s="4">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D178" s="4">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179" s="4">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" s="4">
+        <v>12.23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" s="4">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" s="4">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D183" s="4">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D184" s="4">
+        <v>13.01</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="4">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C186" s="3"/>
+      <c r="D186" s="4"/>
+    </row>
+    <row r="187" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D187" s="4">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D188" s="4">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D189" s="4">
+        <v>19.88</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" s="4">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" s="4">
+        <v>12.29</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" s="4">
+        <v>25.44</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" s="4">
+        <v>12.27</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D194" s="4">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D195" s="4">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D196" s="4">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" s="4">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D198" s="4">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D199" s="4">
+        <v>12.56</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D200" s="4">
+        <v>25.28</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" s="4">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" s="4">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D203" s="4">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D204" s="4">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="4">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" s="4">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D207" s="4">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D208" s="4">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D209" s="4">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D210" s="4">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D211" s="4">
+        <v>12.23</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D212" s="4">
+        <v>12.21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D213" s="4">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D214" s="4">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D215" s="4">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216" s="4">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D217" s="4">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D218" s="4">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D219" s="4">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D220" s="4">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221" s="4">
+        <v>12.29</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222" s="4">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D223" s="4">
+        <v>25.44</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D224" s="4">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D225" s="4">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D226" s="4">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D227" s="4">
+        <v>21.33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228" s="4">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D229" s="4">
+        <v>25.02</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D230" s="4">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D231" s="4">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D232" s="4">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233" s="4">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D234" s="4">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235" s="4">
+        <v>61.48</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D236" s="4">
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D237" s="4">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" s="4">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D239" s="4">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" s="4">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" s="4">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" s="4">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D243" s="4">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D244" s="4">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D245" s="4">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D246" s="4">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D247" s="4">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D248" s="4">
+        <v>12.31</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D249" s="4">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D250" s="4">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D251" s="4">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D252" s="4">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D253" s="4">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D254" s="4">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D255" s="4">
+        <v>26.38</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D256" s="4">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D257" s="4">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" s="4">
+        <v>25.78</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D259" s="4">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D260" s="4">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" s="4">
+        <v>25.83</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D262" s="4">
+        <v>25.95</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D263" s="4">
+        <v>26.19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D264" s="4">
+        <v>26.19</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D265" s="4">
+        <v>25.43</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" s="4">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D267" s="4">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D268" s="4">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D269" s="4">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D270" s="4">
+        <v>36.42</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D271" s="4">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D272" s="4">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D273" s="4">
+        <v>12.27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D274" s="4">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D275" s="4">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D276" s="4">
+        <v>19.57</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D277" s="4">
+        <v>19.690000000000001</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D278" s="4">
+        <v>19.97</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D279" s="4">
+        <v>14.62</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D280" s="4">
+        <v>14.67</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D281" s="4">
+        <v>108.96</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D282" s="4">
+        <v>25.06</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D283" s="4">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D284" s="4">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D285" s="4">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D286" s="4">
+        <v>25.14</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D287" s="4">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D288" s="4">
+        <v>25.53</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D289" s="4">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D290" s="4">
+        <v>59.57</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D291" s="4">
+        <v>22.59</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D292" s="4">
+        <v>23.32</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D293" s="4">
+        <v>23.53</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D294" s="4">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D295" s="4">
+        <v>23.48</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D296" s="4">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D297" s="4">
+        <v>13.49</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D298" s="4">
+        <v>12.29</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D299" s="4">
+        <v>23.12</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D300" s="4">
+        <v>34.94</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D301" s="4">
+        <v>29.87</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D302" s="4">
+        <v>26.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D302" xr:uid="{A54D64F5-758C-46F4-940C-780DD1148CB9}"/>
+  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H541"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/gebaeudedaten.xlsx
+++ b/gebaeudedaten.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objekt 01" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schweden" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objekt 02" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objekt 03" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objekt 04" sheetId="4" state="visible" r:id="rId4"/>

--- a/gebaeudedaten.xlsx
+++ b/gebaeudedaten.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schweden" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Köpi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6731,4 +6732,4792 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D217"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Gebäude</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Geschoss</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Raum Nr.</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Raumbezeichnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.02a</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fahrzeugverkehrsflächen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fahrzeugverkehrsflächen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01.01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Elektrische Stromversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01.01a</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Elektrische Stromversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01.02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01.03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01.04 (*)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Elektrische Stromversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01.05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01.06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01.07</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01.08</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01.08a</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01.09</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01.09a</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Elektrische Stromversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01.11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01.12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Heizung u. Brauchwassererwärmung</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01.12a</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01.13</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01.14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>01.15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verkaufsräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1.01a</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.01b</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Verkaufsräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2.02a</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2.02b</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Teeküche</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2.04a</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2.04c</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Teeküche</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Künstleratelier</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.02a</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.02b</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.02c</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.04a</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.04b</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4.02a</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.02b</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Teeküche</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Besprechungsraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.07a</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4.07b</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4.07c</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Künstleratelier</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>4.08a</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Aufzugs- und Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>_Nicht genutzte Fläche [NUF 1] (v11-Import)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Aufzugs- und Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A 1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A 2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FT 1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FT 1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FT 1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FT 1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FT 2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FT 2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FT 2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FT 2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TH 1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TH 2</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>4.08a</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>3.05a</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4.06a</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.03a</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1.03b</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2.05a</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2.05b</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3.01a</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Gebäude 1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3.01b</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Gebäude 3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gebäude 3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Gebäude 3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Büroräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Vorraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1.03a</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1.03b</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Garderoben</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Werkstätten</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2.05a</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2.05b</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Vorraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.03a</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.03b</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Pausenraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Eingangshalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>4.09a</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>4.09b</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Büroräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Aufzugs- und Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sanitärräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Büroräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>A 3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>A 3</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>A 3</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>A 3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>A 3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Schächte für Förderanlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FT 3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FT 3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>FT 3</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FT 3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Fluchttreppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>TH 3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Erdgeschoß</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TH 4</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>THK 1</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>THK 2</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Treppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>U.01</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sonstige betriebstechnische Anlagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>U.02</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Elektrische Stromversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>U.03</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Heizung u. Brauchwassererwärmung</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>U.04</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>U.05</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>U.06</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>U.07</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Lager</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>U.08</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>U.09</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>U.10</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>U.11</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>U.12</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1. Untergeschoß</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>U.13</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Lagerräume</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.02a</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.02a</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.02b</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.02c</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.02d</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.02e</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.02f</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Flure allgem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3.02g</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.02h</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.02i</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.02j</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Gebäude 4</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>3. Obergeschoß</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.02k</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Büroraum</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>